--- a/Alextor.RAG/Libs/Extractor/Extractor.Test/Files/xlsx1.xlsx
+++ b/Alextor.RAG/Libs/Extractor/Extractor.Test/Files/xlsx1.xlsx
@@ -21,9 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Shhet 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlink</t>
   </si>
   <si>
     <t xml:space="preserve">qwd</t>
@@ -39,7 +42,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -60,6 +63,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,12 +114,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -136,9 +150,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>538200</xdr:colOff>
+      <xdr:colOff>537840</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>95040</xdr:rowOff>
+      <xdr:rowOff>94680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -152,7 +166,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="378000" y="688680"/>
-          <a:ext cx="2598480" cy="1194480"/>
+          <a:ext cx="2598120" cy="1194120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -323,28 +337,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1" s="1" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="testlink"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
